--- a/analise_eua/semicondutores/micron/mu_10q.xlsx
+++ b/analise_eua/semicondutores/micron/mu_10q.xlsx
@@ -22,13 +22,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -39,7 +42,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -47,13 +50,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,774 +433,810 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>45988</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45806</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45715</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45624</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45442</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45351</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45260</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45078</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>44987</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44896</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44714</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44623</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44532</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44350</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44259</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44168</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>43979</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43888</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43797</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Cash and Cash Equivalents</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>13908</v>
+      </c>
+      <c r="C2" t="n">
         <v>9731</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>10163</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>7552</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>6693</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>7594</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>8016</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>8075</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>9298</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>9798</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>9574</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>9157</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>9116</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>8680</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>7759</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>6507</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>5985</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>8267</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>7118</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>6969</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Marketable Securities, Current</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>681</v>
+      </c>
+      <c r="C3" t="n">
         <v>587</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>648</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>663</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>895</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>785</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>990</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>973</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1054</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>1020</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>1007</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1070</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1006</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>900</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>590</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>677</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>1047</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>391</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>363</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>619</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Receivables, Net, Current</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>17314</v>
+      </c>
+      <c r="C4" t="n">
         <v>10184</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>7436</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>6504</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>7423</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>5131</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>4296</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>2943</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2429</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>2278</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>3318</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>6229</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>5384</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>5250</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>4231</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3353</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>3691</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>3603</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3049</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>3419</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Inventory, Net</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>8267</v>
+      </c>
+      <c r="C5" t="n">
         <v>8205</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>8727</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>9007</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>8705</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>8512</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>8443</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>8276</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>8238</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>8129</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>8359</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>5629</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>5383</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>4827</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>4537</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>4743</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>5521</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>5405</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5208</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>4943</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Other Assets, Current</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1243</v>
+      </c>
+      <c r="C6" t="n">
         <v>958</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>945</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>963</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>777</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>1297</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1690</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>791</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>715</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>673</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>663</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>608</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>600</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>521</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>478</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>538</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>285</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>233</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>238</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>217</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Assets, Current</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>41413</v>
+      </c>
+      <c r="C7" t="n">
         <v>29665</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>27919</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>24689</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>24493</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>23319</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>23435</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>21058</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>21734</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>21898</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>22921</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>22708</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>21502</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>20191</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>18561</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>17279</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>16529</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>17899</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>15976</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>16167</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Debt Securities, Available-for-sale, Noncurrent</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>2038</v>
+      </c>
+      <c r="C8" t="n">
         <v>1697</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>1402</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>1375</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1156</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>775</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>627</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>720</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>973</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>1212</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>1426</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1646</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1717</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>1817</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>1399</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>1316</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>1264</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>577</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>586</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>599</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Property, Plant, and Equipment and Finance Lease Right-of-Use Asset, after Accumulated Depreciation and Amortization</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>51408</v>
+      </c>
+      <c r="C9" t="n">
         <v>48477</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>44773</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>42528</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>41476</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>37926</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>37587</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>37677</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>38727</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>39085</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>39335</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>36665</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>36171</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>35155</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>32209</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>31848</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>32229</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>30081</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>29647</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>29352</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Operating Lease, Right-of-Use Asset</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>684</v>
+      </c>
+      <c r="C10" t="n">
         <v>700</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>628</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>637</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>622</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>660</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>642</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>648</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>655</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>673</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>693</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>690</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>587</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>574</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>558</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>575</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>577</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>599</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>605</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>608</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Intangible Assets, Net (Excluding Goodwill)</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>468</v>
+      </c>
+      <c r="C11" t="n">
         <v>465</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>426</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>423</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>419</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>413</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>414</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>416</v>
-      </c>
-      <c r="I11" t="n">
-        <v>410</v>
       </c>
       <c r="J11" t="n">
         <v>410</v>
       </c>
       <c r="K11" t="n">
+        <v>410</v>
+      </c>
+      <c r="L11" t="n">
         <v>428</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>415</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>414</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>347</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>350</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>342</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>336</v>
-      </c>
-      <c r="R11" t="n">
-        <v>332</v>
       </c>
       <c r="S11" t="n">
         <v>332</v>
       </c>
       <c r="T11" t="n">
+        <v>332</v>
+      </c>
+      <c r="U11" t="n">
         <v>333</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Deferred Income Tax Assets, Net</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>680</v>
+      </c>
+      <c r="C12" t="n">
         <v>641</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>483</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>552</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>474</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>597</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>664</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>781</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>708</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>697</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>672</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>682</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>762</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>746</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>822</v>
-      </c>
-      <c r="P12" t="n">
-        <v>726</v>
       </c>
       <c r="Q12" t="n">
         <v>726</v>
       </c>
       <c r="R12" t="n">
+        <v>726</v>
+      </c>
+      <c r="S12" t="n">
         <v>775</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>764</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>783</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Goodwill</t>
         </is>
@@ -1213,10 +1263,10 @@
         <v>1150</v>
       </c>
       <c r="I13" t="n">
+        <v>1150</v>
+      </c>
+      <c r="J13" t="n">
         <v>1252</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1228</v>
       </c>
       <c r="K13" t="n">
         <v>1228</v>
@@ -1248,649 +1298,682 @@
       <c r="T13" t="n">
         <v>1228</v>
       </c>
+      <c r="U13" t="n">
+        <v>1228</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Other Assets, Noncurrent</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>3668</v>
+      </c>
+      <c r="C14" t="n">
         <v>3176</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>1616</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>1699</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>1671</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>1415</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1199</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1326</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1221</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>1317</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>1171</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1262</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1315</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>1188</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>816</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>821</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>802</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>514</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>510</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>579</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Assets</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>101509</v>
+      </c>
+      <c r="C15" t="n">
         <v>85971</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>78397</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>73053</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>71461</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>66255</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>65718</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>63776</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>65680</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>66520</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>67874</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>65296</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>63696</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>61246</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>55943</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>54135</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>53691</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>52005</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>49648</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>49649</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Accounts Payable and Accrued Liabilities, Current</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>10997</v>
+      </c>
+      <c r="C16" t="n">
         <v>9796</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>8761</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>6176</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>7126</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>5145</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>4680</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>3946</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>4177</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>4310</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>5438</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>5788</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>5650</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>5470</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>4427</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>4550</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>4856</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>5364</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>5077</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>5408</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Debt, Current</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>585</v>
+      </c>
+      <c r="C17" t="n">
         <v>569</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>538</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>504</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>533</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>398</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>344</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>908</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>259</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>237</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>171</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>107</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>123</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>118</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>297</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>323</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>273</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>330</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>237</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>462</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Other Liabilities, Current</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>2714</v>
+      </c>
+      <c r="C18" t="n">
         <v>1695</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>836</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>1197</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>1356</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>1297</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>1235</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>1108</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>668</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>708</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>916</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>1114</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>1145</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>924</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>738</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>560</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>559</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>491</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>508</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>447</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Liabilities, Current</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>14296</v>
+      </c>
+      <c r="C19" t="n">
         <v>12060</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>10135</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>7877</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>9015</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>6840</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>6259</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>5962</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>5104</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>5255</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>6525</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>7009</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>6918</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>6512</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>5462</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>5433</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5688</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>6185</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>5822</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>6317</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Long-term Debt and Lease Obligation</t>
         </is>
       </c>
       <c r="B20" t="n">
+        <v>9557</v>
+      </c>
+      <c r="C20" t="n">
         <v>11187</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>15003</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>13851</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>13252</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>12860</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>13378</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>12597</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>12986</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>12037</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>10094</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>6856</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>6953</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>6904</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6418</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>6298</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>6356</v>
       </c>
       <c r="R20" t="n">
         <v>6356</v>
       </c>
       <c r="S20" t="n">
-        <v>5188</v>
+        <v>6356</v>
       </c>
       <c r="T20" t="n">
         <v>5188</v>
       </c>
+      <c r="U20" t="n">
+        <v>5188</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Operating Lease, Liability, Noncurrent</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>656</v>
+      </c>
+      <c r="C21" t="n">
         <v>669</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>600</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>599</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>588</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>609</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>593</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>601</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>603</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>610</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>625</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>629</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>535</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>523</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>513</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>528</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>529</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>540</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>548</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>511</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Other Liabilities, Noncurrent</t>
         </is>
       </c>
       <c r="B22" t="n">
+        <v>3539</v>
+      </c>
+      <c r="C22" t="n">
         <v>2101</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>1308</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>1257</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>1239</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>1049</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>956</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>1026</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>950</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>832</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>808</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>858</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>741</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>632</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>569</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>552</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>555</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>453</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>383</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>426</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Liabilities</t>
         </is>
       </c>
       <c r="B23" t="n">
+        <v>29050</v>
+      </c>
+      <c r="C23" t="n">
         <v>27165</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>27649</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>24420</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>24664</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>22030</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>21848</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>20891</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>20275</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>19263</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>18568</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>16015</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>15851</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>15338</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>13684</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>13472</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>13784</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>14087</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>12527</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>13051</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Common Stock, Value, Issued</t>
         </is>
@@ -1899,7 +1982,7 @@
         <v>127</v>
       </c>
       <c r="C24" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D24" t="n">
         <v>126</v>
@@ -1908,25 +1991,25 @@
         <v>126</v>
       </c>
       <c r="F24" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" t="n">
         <v>125</v>
       </c>
       <c r="H24" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I24" t="n">
         <v>124</v>
       </c>
       <c r="J24" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K24" t="n">
         <v>123</v>
       </c>
       <c r="L24" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M24" t="n">
         <v>122</v>
@@ -1935,7 +2018,7 @@
         <v>122</v>
       </c>
       <c r="O24" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="P24" t="n">
         <v>120</v>
@@ -1944,7 +2027,7 @@
         <v>120</v>
       </c>
       <c r="R24" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="S24" t="n">
         <v>119</v>
@@ -1952,146 +2035,155 @@
       <c r="T24" t="n">
         <v>119</v>
       </c>
+      <c r="U24" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Additional Paid in Capital, Common Stock</t>
         </is>
       </c>
       <c r="B25" t="n">
+        <v>14092</v>
+      </c>
+      <c r="C25" t="n">
         <v>13610</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>12960</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>12711</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>12317</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>11794</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>11564</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>11217</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>10782</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>10633</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>10335</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>9950</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9816</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>9564</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>9285</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>9234</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>9034</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>8764</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>8725</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>8428</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Retained Earnings (Accumulated Deficit)</t>
         </is>
       </c>
       <c r="B26" t="n">
+        <v>66824</v>
+      </c>
+      <c r="C26" t="n">
         <v>53344</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>45559</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>43839</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>42427</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>40169</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>39997</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>39356</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>42391</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>44426</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>46873</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>45916</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>43407</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>41267</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>36452</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>34723</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>34138</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>32402</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>31602</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>31218</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Treasury Stock, Common, Value</t>
         </is>
       </c>
       <c r="B27" t="n">
+        <v>-8502</v>
+      </c>
+      <c r="C27" t="n">
         <v>-8152</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-7852</v>
       </c>
       <c r="D27" t="n">
         <v>-7852</v>
@@ -2100,7 +2192,7 @@
         <v>-7852</v>
       </c>
       <c r="F27" t="n">
-        <v>-7552</v>
+        <v>-7852</v>
       </c>
       <c r="G27" t="n">
         <v>-7552</v>
@@ -2118,163 +2210,172 @@
         <v>-7552</v>
       </c>
       <c r="L27" t="n">
+        <v>-7552</v>
+      </c>
+      <c r="M27" t="n">
         <v>-6343</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>-5362</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>-4954</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>-3645</v>
-      </c>
-      <c r="P27" t="n">
-        <v>-3495</v>
       </c>
       <c r="Q27" t="n">
         <v>-3495</v>
       </c>
       <c r="R27" t="n">
+        <v>-3495</v>
+      </c>
+      <c r="S27" t="n">
         <v>-3454</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>-3414</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>-3271</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Accumulated Other Comprehensive Income (Loss), Net of Tax</t>
         </is>
       </c>
       <c r="B28" t="n">
+        <v>-82</v>
+      </c>
+      <c r="C28" t="n">
         <v>-123</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>-45</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>-191</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>-221</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>-311</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>-264</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>-260</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>-340</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>-373</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>-473</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>-364</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>-138</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>-91</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>47</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>81</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>110</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>-11</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>-9</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Total Shareholders Equity</t>
         </is>
       </c>
       <c r="B29" t="n">
+        <v>72459</v>
+      </c>
+      <c r="C29" t="n">
         <v>58806</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>50748</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>48633</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>46797</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>44225</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>43870</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>42885</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>45405</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>47257</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>49306</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>49281</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>47845</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>45908</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>42259</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>40663</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>39907</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>37820</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>37023</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>36500</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Unearned Government Assistance Non Current</t>
         </is>
@@ -2283,57 +2384,60 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
         <v>603</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>836</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>570</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>672</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>662</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>705</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>632</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>529</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>516</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>663</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>704</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>767</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>722</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>661</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>656</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>553</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>586</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>609</v>
       </c>
     </row>
@@ -2348,1217 +2452,1274 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T19"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>45988</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45806</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45715</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45624</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45442</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45351</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45260</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45078</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>44987</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44896</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44714</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44623</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44532</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44350</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44259</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44168</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>43979</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43888</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43797</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Revenues</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>23860</v>
+      </c>
+      <c r="C2" t="n">
         <v>13643</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>9301</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>8053</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>8709</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>6811</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>5824</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>4726</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>3752</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>3693</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>4085</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>8642</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>7786</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>7687</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>7422</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>6236</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>5773</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>5438</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>4797</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>5144</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Cost of Goods and Services Sold</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>6105</v>
+      </c>
+      <c r="C3" t="n">
         <v>5997</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>5793</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>5090</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>5361</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>4979</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>4745</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>4761</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>4420</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>4899</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>3192</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>4607</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>4110</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>4122</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>4296</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>4587</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4037</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>3675</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>3442</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>3778</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>17755</v>
+      </c>
+      <c r="C4" t="n">
         <v>7646</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>3508</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>2963</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>3348</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>1832</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1079</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>-35</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>-668</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>-1206</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>893</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>4035</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>3676</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>3565</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>3126</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>1649</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>1736</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>1763</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1355</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1366</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Research and Development</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C5" t="n">
         <v>1171</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>965</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>898</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>888</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>850</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>832</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>845</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>758</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>788</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>849</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>773</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>792</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>712</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>670</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>641</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>647</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>649</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>681</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>640</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Selling, General and Administrative Expense</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>344</v>
+      </c>
+      <c r="C6" t="n">
         <v>337</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>318</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>285</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>288</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>291</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>280</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>263</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>219</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>231</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>251</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>264</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>263</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>259</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>230</v>
-      </c>
-      <c r="P6" t="n">
-        <v>214</v>
       </c>
       <c r="Q6" t="n">
         <v>214</v>
       </c>
       <c r="R6" t="n">
+        <v>214</v>
+      </c>
+      <c r="S6" t="n">
         <v>216</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>223</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>211</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Other Operating Income (Expense), Net</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>26</v>
+      </c>
+      <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>56</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>7</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>-2</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>-28</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-224</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>-15</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>48</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>-8</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>-11</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>-6</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>70</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>-75</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>-26</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>131</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>9</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>10</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>11</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>-3</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Operating Income</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>16135</v>
+      </c>
+      <c r="C8" t="n">
         <v>6136</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>2169</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>1773</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>2174</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>719</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>191</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>-1128</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>-1761</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>-2303</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>-209</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>3004</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>2546</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2631</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>1799</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>663</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>866</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>888</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>440</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>518</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Investment Income, Net</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>155</v>
+      </c>
+      <c r="C9" t="n">
         <v>139</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>135</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>108</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>107</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>136</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>130</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>132</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>127</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>119</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>88</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>20</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>12</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>10</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>8</v>
-      </c>
-      <c r="P9" t="n">
-        <v>10</v>
       </c>
       <c r="Q9" t="n">
         <v>10</v>
       </c>
       <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
         <v>23</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>34</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>InterestExpenseNonoperating</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-32</v>
+      </c>
+      <c r="C10" t="n">
         <v>-74</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>-123</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>-112</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-118</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-150</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-144</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-132</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>-119</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>-89</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-51</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-44</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>-55</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-45</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-46</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>-42</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>-48</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>-51</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>-46</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-47</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Other Nonoperating Income (Expense)</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-98</v>
+      </c>
+      <c r="C11" t="n">
         <v>-140</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>-68</v>
-      </c>
-      <c r="D11" t="n">
-        <v>-11</v>
       </c>
       <c r="E11" t="n">
         <v>-11</v>
       </c>
       <c r="F11" t="n">
+        <v>-11</v>
+      </c>
+      <c r="G11" t="n">
         <v>10</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>-7</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-27</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
       <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>-4</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>8</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>6</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>-75</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>45</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>4</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>13</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>10</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>-1</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>46</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Income Before Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>16160</v>
+      </c>
+      <c r="C12" t="n">
         <v>6061</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>2113</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>1758</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>2152</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>715</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>170</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-1155</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>-1753</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>-2271</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-176</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>2988</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2509</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2521</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>1806</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>635</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>841</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>870</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>427</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>561</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>-2371</v>
+      </c>
+      <c r="C13" t="n">
         <v>-829</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>-235</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>-177</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>-283</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>-377</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>622</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>-73</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-139</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>-54</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>-8</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>-358</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>-255</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>-219</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>-65</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>-48</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>-51</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>-68</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-21</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>-55</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Income (Loss) from Equity Method Investments</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>-4</v>
+      </c>
+      <c r="C14" t="n">
         <v>8</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>7</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>2</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>-6</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>-6</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>-4</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>13</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>-11</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>-4</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>9</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>4</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>-6</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>16</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>13</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>3</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Net Income</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>13785</v>
+      </c>
+      <c r="C15" t="n">
         <v>5240</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>1885</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>1583</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>1870</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>332</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>793</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>-1234</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>-1896</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>-2312</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-195</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>2626</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>2263</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>2306</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1735</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>603</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>803</v>
       </c>
       <c r="R15" t="n">
         <v>803</v>
       </c>
       <c r="S15" t="n">
+        <v>803</v>
+      </c>
+      <c r="T15" t="n">
         <v>405</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>491</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Earnings Per Share, Basic</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="C16" t="n">
         <v>4.66</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>1.69</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>1.42</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>1.68</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>0.3</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>0.72</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>-1.12</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>-1.73</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>-2.12</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>-0.18</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>2.36</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>2.02</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>2.06</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>1.55</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>0.54</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.72</v>
       </c>
       <c r="R16" t="n">
         <v>0.72</v>
       </c>
       <c r="S16" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="T16" t="n">
         <v>0.37</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>0.44</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Earnings Per Share, Diluted</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="C17" t="n">
         <v>4.6</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>1.68</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>1.41</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>1.67</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>0.3</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>0.71</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>-1.12</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-1.73</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>-2.12</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>-0.18</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>2.34</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>2</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>2.04</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1.52</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>0.53</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.71</v>
       </c>
       <c r="R17" t="n">
         <v>0.71</v>
       </c>
       <c r="S17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="T17" t="n">
         <v>0.36</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>0.43</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Number of Shares - Basic</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>1126</v>
+      </c>
+      <c r="C18" t="n">
         <v>1125</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>1118</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>1115</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>1111</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>1107</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>1104</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>1100</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>1094</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>1091</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>1090</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>1112</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1119</v>
       </c>
       <c r="N18" t="n">
         <v>1119</v>
       </c>
       <c r="O18" t="n">
+        <v>1119</v>
+      </c>
+      <c r="P18" t="n">
         <v>1121</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>1120</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>1115</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1111</v>
       </c>
       <c r="S18" t="n">
         <v>1111</v>
       </c>
       <c r="T18" t="n">
+        <v>1111</v>
+      </c>
+      <c r="U18" t="n">
         <v>1107</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>Number of Shares - Diluted</t>
         </is>
       </c>
       <c r="B19" t="n">
+        <v>1142</v>
+      </c>
+      <c r="C19" t="n">
         <v>1138</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>1125</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>1123</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>1122</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>1123</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>1114</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1100</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1094</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>1091</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1090</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>1121</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1130</v>
       </c>
       <c r="N19" t="n">
         <v>1130</v>
       </c>
       <c r="O19" t="n">
+        <v>1130</v>
+      </c>
+      <c r="P19" t="n">
         <v>1145</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>1144</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>1135</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>1129</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>1133</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>1129</v>
       </c>
     </row>
@@ -3573,482 +3734,503 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T36"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>45988</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45806</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45715</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45624</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45442</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45351</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45260</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45078</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>44987</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44896</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44714</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44623</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44532</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44350</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44259</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44168</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>43979</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43888</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43797</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Net Income (Loss) Attributable to Parent</t>
         </is>
       </c>
       <c r="B2" t="n">
+        <v>19025</v>
+      </c>
+      <c r="C2" t="n">
         <v>5240</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>5338</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>3453</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>1870</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>-109</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>-441</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>-1234</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>-4403</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>-2507</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>-195</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>7195</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>4569</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>2306</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>3141</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>1406</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>803</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>1720</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>915</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>508</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Depreciation, Depletion and Amortization</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>4498</v>
+      </c>
+      <c r="C3" t="n">
         <v>2212</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>6203</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>4109</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>2030</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>5794</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>3839</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1915</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5819</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>3863</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>1921</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>5234</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>3413</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>1671</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>4593</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>3036</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>1487</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>4083</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>2661</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1296</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Share-based Payment Arrangement, Noncash Expense</t>
         </is>
       </c>
       <c r="B4" t="n">
+        <v>599</v>
+      </c>
+      <c r="C4" t="n">
         <v>290</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>722</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>469</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>220</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>620</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>401</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>188</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>448</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>303</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>146</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>378</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>247</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>118</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>285</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>189</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>92</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>239</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>157</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>72</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Receivables</t>
         </is>
       </c>
       <c r="B5" t="n">
+        <v>-8298</v>
+      </c>
+      <c r="C5" t="n">
         <v>-871</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>-123</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>338</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>-817</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-2562</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>-1759</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>-501</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>2728</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>2910</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1842</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>-906</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>-44</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>67</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>-340</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>533</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>251</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>-461</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>104</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>-208</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Inventories</t>
         </is>
       </c>
       <c r="B6" t="n">
+        <v>88</v>
+      </c>
+      <c r="C6" t="n">
         <v>150</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>148</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>-132</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>170</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-125</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-57</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>111</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>-3406</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>-2896</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>-1697</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>-1146</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>-900</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>-344</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>814</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>629</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>86</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>-286</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-90</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>175</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Accounts Payable and Accrued Liabilities</t>
         </is>
       </c>
       <c r="B7" t="n">
+        <v>928</v>
+      </c>
+      <c r="C7" t="n">
         <v>156</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>38</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>-714</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>-241</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>846</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>573</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>271</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>-1764</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>-1795</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>-1056</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>382</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>107</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>-42</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>-309</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>-777</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>-753</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>700</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>257</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>178</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Other Current Liabilities</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>1469</v>
+      </c>
+      <c r="C8" t="n">
         <v>449</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>-681</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>-321</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>-161</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>769</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>706</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>579</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
@@ -4082,31 +4264,34 @@
       <c r="T8" t="n">
         <v>0</v>
       </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Other Noncurrent Liabilities</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>2106</v>
+      </c>
+      <c r="C9" t="n">
         <v>547</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>-681</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>132</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>769</v>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
@@ -4146,695 +4331,728 @@
       <c r="T9" t="n">
         <v>0</v>
       </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Other Operating Activities, Cash Flow Statement</t>
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-101</v>
+      </c>
+      <c r="C10" t="n">
         <v>238</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>356</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>188</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>173</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>304</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>157</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>72</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>57</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>-22</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-18</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>141</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>91</v>
-      </c>
-      <c r="N10" t="n">
-        <v>25</v>
       </c>
       <c r="O10" t="n">
         <v>25</v>
       </c>
       <c r="P10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="n">
         <v>4</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>18</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>34</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>-4</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Net Cash Provided by (Used in) Operating Activities</t>
         </is>
       </c>
       <c r="B11" t="n">
+        <v>20314</v>
+      </c>
+      <c r="C11" t="n">
         <v>8411</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>11795</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>7186</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>3244</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>5102</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>2620</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>1401</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>1310</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>1286</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>943</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>11404</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>7566</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>3938</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>8584</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>5024</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>1967</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>6035</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>4012</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>2011</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Purchases Of Property And Equipment And Intangible Assets</t>
         </is>
       </c>
       <c r="B12" t="n">
+        <v>-11776</v>
+      </c>
+      <c r="C12" t="n">
         <v>-5389</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>-10199</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>-7261</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-3206</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>-5266</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-3180</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-1796</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>-6215</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>-4654</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-2449</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>-8454</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>-5876</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>-3265</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>-8015</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>-5756</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>-2738</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>-5943</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>-3999</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>-1943</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Payments to Acquire Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>-1120</v>
+      </c>
+      <c r="C13" t="n">
         <v>-255</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>-1203</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>-816</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>-377</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>-1110</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>-465</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>-199</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-496</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>-293</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>-90</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>-1359</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>-922</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>-528</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>-1919</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>-1349</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>-1002</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>-793</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-566</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>-407</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Proceeds From Government Assistance</t>
         </is>
       </c>
       <c r="B14" t="n">
+        <v>2256</v>
+      </c>
+      <c r="C14" t="n">
         <v>878</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>1294</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>1028</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>65</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>267</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>234</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>85</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>248</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>64</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>104</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>66</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>55</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>335</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>176</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>40</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>140</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>105</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Sale and Maturity of Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>701</v>
+      </c>
+      <c r="C15" t="n">
         <v>268</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>1249</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>874</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>428</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>1433</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>726</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>374</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>1170</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>765</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>358</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>964</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>631</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>313</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1024</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>746</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>216</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>636</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>523</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>163</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Payments for (Proceeds from) Other Investing Activities</t>
         </is>
       </c>
       <c r="B16" t="n">
+        <v>-180</v>
+      </c>
+      <c r="C16" t="n">
         <v>-96</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>-30</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>-125</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>-58</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>-35</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>-24</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>-22</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>-90</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>-71</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>-91</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>-162</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>-140</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>-77</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>47</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>31</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>21</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>-48</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>-21</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-12</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Net Cash Provided by (Used in) Investing Activities</t>
         </is>
       </c>
       <c r="B17" t="n">
+        <v>-10119</v>
+      </c>
+      <c r="C17" t="n">
         <v>-4594</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>-8889</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>-6300</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>-3148</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>-4711</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>-2709</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>-1558</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-5361</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>-4181</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>-2266</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>-7761</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-5176</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>-2485</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>-8055</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>-5974</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>-3418</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>-4851</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>-2899</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>-1189</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Repayment of Long-term Debt, Long-term Lease Obligation, and Capital Security</t>
         </is>
       </c>
       <c r="B18" t="n">
+        <v>-4626</v>
+      </c>
+      <c r="C18" t="n">
         <v>-2943</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>-3604</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>-2626</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>-84</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>-1816</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>-1101</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>-53</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>-706</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>-53</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>-20</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>-2008</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>-1981</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>-1949</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>-1344</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>-103</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>-84</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>-4286</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-1676</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-1415</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Payments for Repurchase of Common Stock</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>-650</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-300</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-425</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-425</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-425</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-1648</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-667</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-259</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-203</v>
+      </c>
+      <c r="T19" t="n">
+        <v>-159</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-89</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B20" t="n">
+        <v>-545</v>
+      </c>
+      <c r="C20" t="n">
         <v>-367</v>
       </c>
-      <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>-116</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N20" t="n">
         <v>-112</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O20" t="n">
         <v>-102</v>
       </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Payments for Repurchase of Common Stock</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>-300</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-425</v>
-      </c>
-      <c r="J20" t="n">
-        <v>-425</v>
-      </c>
-      <c r="K20" t="n">
-        <v>-425</v>
-      </c>
-      <c r="L20" t="n">
-        <v>-1648</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-667</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-259</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
@@ -4842,63 +5060,66 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-203</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-159</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-89</v>
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Payments of Dividends</t>
         </is>
       </c>
       <c r="B21" t="n">
+        <v>-266</v>
+      </c>
+      <c r="C21" t="n">
         <v>-134</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>-392</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>-261</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>-131</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>-384</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>-256</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>-129</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>-378</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>-252</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>-126</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>-335</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>-224</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>-112</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
@@ -4914,964 +5135,1079 @@
       <c r="T21" t="n">
         <v>0</v>
       </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Proceeds from Issuance of Long-term Debt</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4430</v>
+      </c>
+      <c r="E22" t="n">
+        <v>2682</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>999</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6716</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5221</v>
+      </c>
+      <c r="L22" t="n">
+        <v>3349</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1188</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1250</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>Proceeds from (Payments for) Other Financing Activities</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B23" t="n">
+        <v>175</v>
+      </c>
+      <c r="C23" t="n">
         <v>-1</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D23" t="n">
         <v>-220</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E23" t="n">
         <v>-121</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F23" t="n">
         <v>-207</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G23" t="n">
         <v>-40</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H23" t="n">
         <v>-18</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I23" t="n">
         <v>-114</v>
       </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
         <v>19</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L23" t="n">
         <v>-99</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M23" t="n">
         <v>99</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N23" t="n">
         <v>110</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O23" t="n">
         <v>-13</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P23" t="n">
         <v>-142</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q23" t="n">
         <v>17</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R23" t="n">
         <v>-33</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S23" t="n">
         <v>147</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T23" t="n">
         <v>151</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U23" t="n">
         <v>17</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>Net Cash Provided by (Used in) Financing Activities</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B24" t="n">
+        <v>-5912</v>
+      </c>
+      <c r="C24" t="n">
         <v>-3745</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D24" t="n">
         <v>214</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E24" t="n">
         <v>-326</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F24" t="n">
         <v>-422</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G24" t="n">
         <v>-1368</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H24" t="n">
         <v>-458</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I24" t="n">
         <v>-352</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J24" t="n">
         <v>5095</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K24" t="n">
         <v>4434</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L24" t="n">
         <v>2632</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M24" t="n">
         <v>-2140</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N24" t="n">
         <v>-979</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O24" t="n">
         <v>-513</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P24" t="n">
         <v>-437</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q24" t="n">
         <v>-209</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R24" t="n">
         <v>-214</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S24" t="n">
         <v>-135</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T24" t="n">
         <v>-1207</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U24" t="n">
         <v>-992</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>Effect of Exchange Rate on Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B25" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" t="n">
         <v>14</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D25" t="n">
         <v>-3</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E25" t="n">
         <v>-49</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F25" t="n">
         <v>-29</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G25" t="n">
         <v>-15</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H25" t="n">
         <v>-8</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I25" t="n">
         <v>-1</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J25" t="n">
         <v>-13</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K25" t="n">
         <v>9</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L25" t="n">
         <v>-6</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M25" t="n">
         <v>-71</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N25" t="n">
         <v>-16</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O25" t="n">
         <v>-6</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P25" t="n">
         <v>44</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q25" t="n">
         <v>43</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R25" t="n">
         <v>27</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S25" t="n">
         <v>-8</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T25" t="n">
         <v>-14</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U25" t="n">
         <v>-14</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B26" t="n">
+        <v>4288</v>
+      </c>
+      <c r="C26" t="n">
         <v>86</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D26" t="n">
         <v>3117</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E26" t="n">
         <v>511</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F26" t="n">
         <v>-355</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G26" t="n">
         <v>-992</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H26" t="n">
         <v>-555</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I26" t="n">
         <v>-510</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J26" t="n">
         <v>1031</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K26" t="n">
         <v>1548</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L26" t="n">
         <v>1303</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M26" t="n">
         <v>1432</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N26" t="n">
         <v>1395</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O26" t="n">
         <v>934</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P26" t="n">
         <v>136</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q26" t="n">
         <v>-1116</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R26" t="n">
         <v>-1638</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S26" t="n">
         <v>1041</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T26" t="n">
         <v>-108</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U26" t="n">
         <v>-184</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B27" t="n">
         <v>9646</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C27" t="n">
+        <v>9646</v>
+      </c>
+      <c r="D27" t="n">
         <v>7052</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E27" t="n">
         <v>7052</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F27" t="n">
         <v>7052</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G27" t="n">
         <v>8656</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H27" t="n">
         <v>8656</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I27" t="n">
         <v>8656</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J27" t="n">
         <v>8339</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K27" t="n">
         <v>8339</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L27" t="n">
         <v>8339</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M27" t="n">
         <v>7829</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N27" t="n">
         <v>7829</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O27" t="n">
         <v>7829</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P27" t="n">
         <v>7690</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q27" t="n">
         <v>7690</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R27" t="n">
         <v>7690</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S27" t="n">
         <v>7279</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T27" t="n">
         <v>7279</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U27" t="n">
         <v>7279</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Right-of-Use Asset Obtained in Exchange for Finance Lease Liability</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>11</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Other Current Assets</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="n">
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
         <v>-206</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E29" t="n">
         <v>-204</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
         <v>-435</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H29" t="n">
         <v>-799</v>
       </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Proceeds from Issuance of Long-term Debt</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="n">
-        <v>4430</v>
-      </c>
-      <c r="D28" t="n">
-        <v>2682</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>999</v>
-      </c>
-      <c r="G28" t="n">
-        <v>999</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>6716</v>
-      </c>
-      <c r="J28" t="n">
-        <v>5221</v>
-      </c>
-      <c r="K28" t="n">
-        <v>3349</v>
-      </c>
-      <c r="L28" t="n">
-        <v>2000</v>
-      </c>
-      <c r="M28" t="n">
-        <v>2000</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2000</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1188</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="S28" t="n">
-        <v>1250</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>Payments On Equipment Purchase Contracts</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" t="n">
+      <c r="B30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
         <v>-127</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H30" t="n">
         <v>-82</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I30" t="n">
         <v>-56</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J30" t="n">
         <v>-112</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K30" t="n">
         <v>-76</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L30" t="n">
         <v>-47</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M30" t="n">
         <v>-132</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N30" t="n">
         <v>-105</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O30" t="n">
         <v>-78</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P30" t="n">
         <v>-139</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q30" t="n">
         <v>-123</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R30" t="n">
         <v>-97</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S30" t="n">
         <v>-49</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T30" t="n">
         <v>-29</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U30" t="n">
         <v>-11</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Inventory Write-down</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="B31" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
         <v>1831</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K31" t="n">
         <v>1430</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Gain (Loss) on Extinguishment of Debt</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="B32" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>83</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N32" t="n">
         <v>83</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O32" t="n">
         <v>83</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P32" t="n">
         <v>1</v>
       </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>-40</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T32" t="n">
         <v>-42</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U32" t="n">
         <v>-42</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Sale of Debt Securities, Available-for-sale</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
         <v>22</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K33" t="n">
         <v>8</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L33" t="n">
         <v>4</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M33" t="n">
         <v>258</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N33" t="n">
         <v>172</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O33" t="n">
         <v>124</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P33" t="n">
         <v>473</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q33" t="n">
         <v>178</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R33" t="n">
         <v>45</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S33" t="n">
         <v>1157</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T33" t="n">
         <v>1059</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U33" t="n">
         <v>988</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Proceeds from Sale of Other Assets, Investing Activities</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="B34" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>888</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N34" t="n">
         <v>893</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O34" t="n">
         <v>893</v>
       </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>Increase (Decrease) in Deferred Income Taxes</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="n">
+      <c r="B35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
         <v>54</v>
       </c>
-      <c r="O34" t="n">
+      <c r="P35" t="n">
         <v>-94</v>
       </c>
-      <c r="P34" t="n">
+      <c r="Q35" t="n">
         <v>-11</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="R35" t="n">
         <v>-24</v>
       </c>
-      <c r="R34" t="n">
+      <c r="S35" t="n">
         <v>26</v>
       </c>
-      <c r="S34" t="n">
+      <c r="T35" t="n">
         <v>38</v>
       </c>
-      <c r="T34" t="n">
+      <c r="U35" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>Amortization of Debt Issuance Costs and Discounts</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" t="n">
+      <c r="B36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
         <v>22</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q36" t="n">
         <v>15</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R36" t="n">
         <v>7</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S36" t="n">
         <v>20</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T36" t="n">
         <v>16</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U36" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Payments to Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
         <v>-744</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T37" t="n">
         <v>-744</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U37" t="n">
         <v>-744</v>
       </c>
     </row>

--- a/analise_eua/semicondutores/micron/mu_10q.xlsx
+++ b/analise_eua/semicondutores/micron/mu_10q.xlsx
@@ -433,68 +433,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U30"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46079</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45988</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45806</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45715</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45624</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45442</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45351</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45260</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45078</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44987</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44896</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44714</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44623</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44532</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44350</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44259</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44168</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43979</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43888</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="V1" s="1" t="n">
         <v>43797</v>
       </c>
     </row>
@@ -505,63 +508,66 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>24995</v>
+      </c>
+      <c r="C2" t="n">
         <v>13908</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>9731</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>10163</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>7552</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>6693</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>7594</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>8016</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>8075</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>9298</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>9798</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>9574</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>9157</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>9116</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>8680</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>7759</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>6507</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>5985</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>8267</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>7118</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>6969</v>
       </c>
     </row>
@@ -572,63 +578,66 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>1027</v>
+      </c>
+      <c r="C3" t="n">
         <v>681</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>587</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>648</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>663</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>895</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>785</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>990</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>973</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>1054</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>1020</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1007</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1070</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>1006</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>900</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>590</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>677</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>1047</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>391</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>363</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>619</v>
       </c>
     </row>
@@ -639,63 +648,66 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>31025</v>
+      </c>
+      <c r="C4" t="n">
         <v>17314</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>10184</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>7436</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>6504</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>7423</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>5131</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>4296</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2943</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>2429</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>2278</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>3318</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>6229</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>5384</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>5250</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>4231</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>3353</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>3691</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>3603</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>3049</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>3419</v>
       </c>
     </row>
@@ -706,63 +718,66 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>8567</v>
+      </c>
+      <c r="C5" t="n">
         <v>8267</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>8205</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>8727</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>9007</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>8705</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>8512</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>8443</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>8276</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>8238</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>8129</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>8359</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>5629</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>5383</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>4827</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>4537</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>4743</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>5521</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>5405</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>5208</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>4943</v>
       </c>
     </row>
@@ -773,63 +788,66 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1123</v>
+      </c>
+      <c r="C6" t="n">
         <v>1243</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>958</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>945</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>963</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>777</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>1297</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1690</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>791</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>715</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>673</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>663</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>608</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>600</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>521</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>478</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>538</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>285</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>233</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>238</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>217</v>
       </c>
     </row>
@@ -840,63 +858,66 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>66737</v>
+      </c>
+      <c r="C7" t="n">
         <v>41413</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>29665</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>27919</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>24689</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>24493</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>23319</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>23435</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>21058</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>21734</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>21898</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>22921</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>22708</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>21502</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>20191</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>18561</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>17279</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>16529</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>17899</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>15976</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>16167</v>
       </c>
     </row>
@@ -907,63 +928,66 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4106</v>
+      </c>
+      <c r="C8" t="n">
         <v>2038</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>1697</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>1402</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1375</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>1156</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>775</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>627</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>720</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>973</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>1212</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1426</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>1646</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>1717</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>1817</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>1399</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>1316</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>1264</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>577</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>586</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>599</v>
       </c>
     </row>
@@ -974,63 +998,66 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>56426</v>
+      </c>
+      <c r="C9" t="n">
         <v>51408</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>48477</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>44773</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>42528</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>41476</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>37926</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>37587</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>37677</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>38727</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>39085</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>39335</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>36665</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>36171</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>35155</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>32209</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>31848</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>32229</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>30081</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>29647</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>29352</v>
       </c>
     </row>
@@ -1041,63 +1068,66 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>683</v>
+      </c>
+      <c r="C10" t="n">
         <v>684</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>700</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>628</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>637</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>622</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>660</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>642</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>648</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>655</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>673</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>693</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>690</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>587</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>574</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>558</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>575</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>577</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>599</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>605</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>608</v>
       </c>
     </row>
@@ -1108,63 +1138,66 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>473</v>
+      </c>
+      <c r="C11" t="n">
         <v>468</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>465</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>426</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>423</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>419</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>413</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>414</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>416</v>
-      </c>
-      <c r="J11" t="n">
-        <v>410</v>
       </c>
       <c r="K11" t="n">
         <v>410</v>
       </c>
       <c r="L11" t="n">
+        <v>410</v>
+      </c>
+      <c r="M11" t="n">
         <v>428</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>415</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>414</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>347</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>350</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>342</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>336</v>
-      </c>
-      <c r="S11" t="n">
-        <v>332</v>
       </c>
       <c r="T11" t="n">
         <v>332</v>
       </c>
       <c r="U11" t="n">
+        <v>332</v>
+      </c>
+      <c r="V11" t="n">
         <v>333</v>
       </c>
     </row>
@@ -1175,63 +1208,66 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>700</v>
+      </c>
+      <c r="C12" t="n">
         <v>680</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>641</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>483</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>552</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>474</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>597</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>664</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>781</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>708</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>697</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>672</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>682</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>762</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>746</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>822</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>726</v>
       </c>
       <c r="R12" t="n">
         <v>726</v>
       </c>
       <c r="S12" t="n">
+        <v>726</v>
+      </c>
+      <c r="T12" t="n">
         <v>775</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>764</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>783</v>
       </c>
     </row>
@@ -1266,10 +1302,10 @@
         <v>1150</v>
       </c>
       <c r="J13" t="n">
+        <v>1150</v>
+      </c>
+      <c r="K13" t="n">
         <v>1252</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1228</v>
       </c>
       <c r="L13" t="n">
         <v>1228</v>
@@ -1301,6 +1337,9 @@
       <c r="U13" t="n">
         <v>1228</v>
       </c>
+      <c r="V13" t="n">
+        <v>1228</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1309,63 +1348,66 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>3837</v>
+      </c>
+      <c r="C14" t="n">
         <v>3668</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>3176</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>1616</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>1699</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>1671</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>1415</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1199</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>1326</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>1221</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>1317</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>1171</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>1262</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>1315</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>1188</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>816</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>821</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>802</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>514</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>510</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>579</v>
       </c>
     </row>
@@ -1376,63 +1418,66 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>134112</v>
+      </c>
+      <c r="C15" t="n">
         <v>101509</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>85971</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>78397</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>73053</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>71461</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>66255</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>65718</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>63776</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>65680</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>66520</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>67874</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>65296</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>63696</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>61246</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>55943</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>54135</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>53691</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>52005</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>49648</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>49649</v>
       </c>
     </row>
@@ -1443,63 +1488,66 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>15521</v>
+      </c>
+      <c r="C16" t="n">
         <v>10997</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>9796</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>8761</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>6176</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>7126</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>5145</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>4680</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>3946</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>4177</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>4310</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>5438</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>5788</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>5650</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>5470</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>4427</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>4550</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>4856</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>5364</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>5077</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>5408</v>
       </c>
     </row>
@@ -1510,63 +1558,66 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>582</v>
+      </c>
+      <c r="C17" t="n">
         <v>585</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>569</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>538</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>504</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>533</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>398</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>344</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>908</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>259</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>237</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>171</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>107</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>123</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>118</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>297</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>323</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>273</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>330</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>237</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>462</v>
       </c>
     </row>
@@ -1577,63 +1628,66 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>3385</v>
+      </c>
+      <c r="C18" t="n">
         <v>2714</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>1695</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>836</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>1197</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>1356</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>1297</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>1235</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>1108</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>668</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>708</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>916</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>1114</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>1145</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>924</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>738</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>560</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>559</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>491</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>508</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>447</v>
       </c>
     </row>
@@ -1644,63 +1698,66 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>19488</v>
+      </c>
+      <c r="C19" t="n">
         <v>14296</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>12060</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>10135</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>7877</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>9015</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>6840</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>6259</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>5962</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>5104</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>5255</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>6525</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>7009</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>6918</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>6512</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>5462</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>5433</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>5688</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>6185</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>5822</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>6317</v>
       </c>
     </row>
@@ -1711,65 +1768,68 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>5140</v>
+      </c>
+      <c r="C20" t="n">
         <v>9557</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>11187</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>15003</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>13851</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>13252</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>12860</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>13378</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>12597</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>12986</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>12037</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>10094</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>6856</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>6953</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>6904</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>6418</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>6298</v>
-      </c>
-      <c r="R20" t="n">
-        <v>6356</v>
       </c>
       <c r="S20" t="n">
         <v>6356</v>
       </c>
       <c r="T20" t="n">
-        <v>5188</v>
+        <v>6356</v>
       </c>
       <c r="U20" t="n">
         <v>5188</v>
       </c>
+      <c r="V20" t="n">
+        <v>5188</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1778,63 +1838,66 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>654</v>
+      </c>
+      <c r="C21" t="n">
         <v>656</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>669</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>600</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>599</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>588</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>609</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>593</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>601</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>603</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>610</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>625</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>629</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>535</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>523</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>513</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>528</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>529</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>540</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>548</v>
       </c>
-      <c r="U21" t="n">
+      <c r="V21" t="n">
         <v>511</v>
       </c>
     </row>
@@ -1845,63 +1908,66 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>7086</v>
+      </c>
+      <c r="C22" t="n">
         <v>3539</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>2101</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>1308</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>1257</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>1239</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>1049</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>956</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>1026</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>950</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>832</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>808</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>858</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>741</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>632</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>569</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>552</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>555</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>453</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>383</v>
       </c>
-      <c r="U22" t="n">
+      <c r="V22" t="n">
         <v>426</v>
       </c>
     </row>
@@ -1912,63 +1978,66 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>33388</v>
+      </c>
+      <c r="C23" t="n">
         <v>29050</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>27165</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>27649</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>24420</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>24664</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>22030</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>21848</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>20891</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>20275</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>19263</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>18568</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>16015</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>15851</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>15338</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>13684</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>13472</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>13784</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>14087</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>12527</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>13051</v>
       </c>
     </row>
@@ -1979,13 +2048,13 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C24" t="n">
         <v>127</v>
       </c>
       <c r="D24" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E24" t="n">
         <v>126</v>
@@ -1994,25 +2063,25 @@
         <v>126</v>
       </c>
       <c r="G24" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H24" t="n">
         <v>125</v>
       </c>
       <c r="I24" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J24" t="n">
         <v>124</v>
       </c>
       <c r="K24" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="L24" t="n">
         <v>123</v>
       </c>
       <c r="M24" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N24" t="n">
         <v>122</v>
@@ -2021,7 +2090,7 @@
         <v>122</v>
       </c>
       <c r="P24" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q24" t="n">
         <v>120</v>
@@ -2030,7 +2099,7 @@
         <v>120</v>
       </c>
       <c r="S24" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="T24" t="n">
         <v>119</v>
@@ -2038,6 +2107,9 @@
       <c r="U24" t="n">
         <v>119</v>
       </c>
+      <c r="V24" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2046,63 +2118,66 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>14442</v>
+      </c>
+      <c r="C25" t="n">
         <v>14092</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>13610</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>12960</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>12711</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>12317</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>11794</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>11564</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>11217</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>10782</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>10633</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>10335</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>9950</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>9816</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>9564</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>9285</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>9234</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>9034</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>8764</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>8725</v>
       </c>
-      <c r="U25" t="n">
+      <c r="V25" t="n">
         <v>8428</v>
       </c>
     </row>
@@ -2113,63 +2188,66 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>94682</v>
+      </c>
+      <c r="C26" t="n">
         <v>66824</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>53344</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>45559</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>43839</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>42427</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>40169</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>39997</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>39356</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>42391</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>44426</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>46873</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>45916</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>43407</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>41267</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>36452</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>34723</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>34138</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>32402</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>31602</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>31218</v>
       </c>
     </row>
@@ -2183,10 +2261,10 @@
         <v>-8502</v>
       </c>
       <c r="C27" t="n">
+        <v>-8502</v>
+      </c>
+      <c r="D27" t="n">
         <v>-8152</v>
-      </c>
-      <c r="D27" t="n">
-        <v>-7852</v>
       </c>
       <c r="E27" t="n">
         <v>-7852</v>
@@ -2195,7 +2273,7 @@
         <v>-7852</v>
       </c>
       <c r="G27" t="n">
-        <v>-7552</v>
+        <v>-7852</v>
       </c>
       <c r="H27" t="n">
         <v>-7552</v>
@@ -2213,30 +2291,33 @@
         <v>-7552</v>
       </c>
       <c r="M27" t="n">
+        <v>-7552</v>
+      </c>
+      <c r="N27" t="n">
         <v>-6343</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>-5362</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>-4954</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>-3645</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-3495</v>
       </c>
       <c r="R27" t="n">
         <v>-3495</v>
       </c>
       <c r="S27" t="n">
+        <v>-3495</v>
+      </c>
+      <c r="T27" t="n">
         <v>-3454</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>-3414</v>
       </c>
-      <c r="U27" t="n">
+      <c r="V27" t="n">
         <v>-3271</v>
       </c>
     </row>
@@ -2247,63 +2328,66 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>-26</v>
+      </c>
+      <c r="C28" t="n">
         <v>-82</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>-123</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>-45</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>-191</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>-221</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>-311</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>-264</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>-260</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>-340</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>-373</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>-473</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>-364</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>-138</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>-91</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>47</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>81</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>110</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>-11</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>-9</v>
       </c>
-      <c r="U28" t="n">
+      <c r="V28" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2314,63 +2398,66 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>100724</v>
+      </c>
+      <c r="C29" t="n">
         <v>72459</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>58806</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>50748</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>48633</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>46797</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>44225</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>43870</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>42885</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>45405</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>47257</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>49306</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>49281</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>47845</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>45908</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>42259</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>40663</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>39907</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>37820</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>37023</v>
       </c>
-      <c r="U29" t="n">
+      <c r="V29" t="n">
         <v>36500</v>
       </c>
     </row>
@@ -2387,57 +2474,60 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
         <v>603</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>836</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>570</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>672</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>662</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>705</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>632</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>529</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>516</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>663</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>704</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>767</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>722</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>661</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>656</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>553</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>586</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>609</v>
       </c>
     </row>
@@ -2452,68 +2542,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:V19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46079</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45988</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45806</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45715</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45624</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45442</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45351</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45260</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45078</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44987</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44896</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44714</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44623</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44532</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44350</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44259</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44168</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43979</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43888</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="V1" s="1" t="n">
         <v>43797</v>
       </c>
     </row>
@@ -2524,63 +2617,66 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>41456</v>
+      </c>
+      <c r="C2" t="n">
         <v>23860</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>13643</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>9301</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>8053</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>8709</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>6811</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>5824</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>4726</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>3752</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>3693</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>4085</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>8642</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>7786</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>7687</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>7422</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>6236</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>5773</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>5438</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>4797</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>5144</v>
       </c>
     </row>
@@ -2591,63 +2687,66 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>6400</v>
+      </c>
+      <c r="C3" t="n">
         <v>6105</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>5997</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>5793</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>5090</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>5361</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>4979</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>4745</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>4761</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>4420</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>4899</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>3192</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>4607</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>4110</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>4122</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>4296</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>4587</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>4037</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>3675</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>3442</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>3778</v>
       </c>
     </row>
@@ -2658,63 +2757,66 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>35056</v>
+      </c>
+      <c r="C4" t="n">
         <v>17755</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>7646</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>3508</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>2963</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>3348</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1832</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>1079</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>-35</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>-668</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>-1206</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>893</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>4035</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>3676</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>3565</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>3126</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>1649</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>1736</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1763</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1355</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>1366</v>
       </c>
     </row>
@@ -2725,63 +2827,66 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>1316</v>
+      </c>
+      <c r="C5" t="n">
         <v>1250</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>1171</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>965</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>898</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>888</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>850</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>832</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>845</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>758</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>788</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>849</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>773</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>792</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>712</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>670</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>641</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>647</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>649</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>681</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>640</v>
       </c>
     </row>
@@ -2792,63 +2897,66 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>407</v>
+      </c>
+      <c r="C6" t="n">
         <v>344</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>337</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>318</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>285</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>288</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>291</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>280</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>263</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>219</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>231</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>251</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>264</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>263</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>259</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>230</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>214</v>
       </c>
       <c r="R6" t="n">
         <v>214</v>
       </c>
       <c r="S6" t="n">
+        <v>214</v>
+      </c>
+      <c r="T6" t="n">
         <v>216</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>223</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>211</v>
       </c>
     </row>
@@ -2859,63 +2967,66 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" t="n">
         <v>26</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>56</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>7</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>-2</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-28</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>-224</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>-15</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>48</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>-8</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>-11</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>-6</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>70</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>-75</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>-26</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>131</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>9</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>10</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>11</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>-3</v>
       </c>
     </row>
@@ -2926,63 +3037,66 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>33318</v>
+      </c>
+      <c r="C8" t="n">
         <v>16135</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>6136</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>2169</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>1773</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>2174</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>719</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>191</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>-1128</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>-1761</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>-2303</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>-209</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>3004</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2546</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>2631</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>1799</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>663</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>866</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>888</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>440</v>
       </c>
-      <c r="U8" t="n">
+      <c r="V8" t="n">
         <v>518</v>
       </c>
     </row>
@@ -2993,63 +3107,66 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>215</v>
+      </c>
+      <c r="C9" t="n">
         <v>155</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>139</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>135</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>108</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>107</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>136</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>130</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>132</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>127</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>119</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>88</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>20</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>12</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>10</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>8</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>10</v>
       </c>
       <c r="R9" t="n">
         <v>10</v>
       </c>
       <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
         <v>23</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>34</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>44</v>
       </c>
     </row>
@@ -3060,63 +3177,66 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
         <v>-32</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>-74</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>-123</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>-112</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-118</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-150</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-144</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>-132</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>-119</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-89</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-51</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>-44</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-55</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-45</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>-46</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>-42</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>-48</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>-51</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-46</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>-47</v>
       </c>
     </row>
@@ -3127,63 +3247,66 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>-321</v>
+      </c>
+      <c r="C11" t="n">
         <v>-98</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>-140</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>-68</v>
-      </c>
-      <c r="E11" t="n">
-        <v>-11</v>
       </c>
       <c r="F11" t="n">
         <v>-11</v>
       </c>
       <c r="G11" t="n">
+        <v>-11</v>
+      </c>
+      <c r="H11" t="n">
         <v>10</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-7</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>-27</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>-4</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>8</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>6</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>-75</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>45</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>4</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>13</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>10</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>-1</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>46</v>
       </c>
     </row>
@@ -3194,63 +3317,66 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>33212</v>
+      </c>
+      <c r="C12" t="n">
         <v>16160</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>6061</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>2113</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>1758</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>2152</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>715</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>170</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>-1155</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>-1753</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-2271</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>-176</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2988</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2509</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>2521</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>1806</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>635</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>841</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>870</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>427</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>561</v>
       </c>
     </row>
@@ -3261,63 +3387,66 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>-4978</v>
+      </c>
+      <c r="C13" t="n">
         <v>-2371</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>-829</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>-235</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>-177</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>-283</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>-377</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>622</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-73</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>-139</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>-54</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>-8</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>-358</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>-255</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>-219</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>-65</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>-48</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>-51</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-68</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>-21</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>-55</v>
       </c>
     </row>
@@ -3328,63 +3457,66 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="n">
         <v>-4</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>8</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>7</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>2</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>-6</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>-6</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>-4</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>13</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>-11</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>-4</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>9</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>4</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>-6</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>16</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>13</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>3</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>2</v>
       </c>
     </row>
@@ -3395,63 +3527,66 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>28243</v>
+      </c>
+      <c r="C15" t="n">
         <v>13785</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>5240</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>1885</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>1583</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>1870</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>332</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>793</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>-1234</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>-1896</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>-2312</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>-195</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>2626</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>2263</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>2306</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>1735</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>603</v>
-      </c>
-      <c r="R15" t="n">
-        <v>803</v>
       </c>
       <c r="S15" t="n">
         <v>803</v>
       </c>
       <c r="T15" t="n">
+        <v>803</v>
+      </c>
+      <c r="U15" t="n">
         <v>405</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>491</v>
       </c>
     </row>
@@ -3462,63 +3597,66 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="C16" t="n">
         <v>12.25</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>4.66</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>1.69</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>1.42</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>1.68</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>0.3</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>0.72</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>-1.12</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>-1.73</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>-2.12</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>-0.18</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>2.36</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>2.02</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>2.06</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>1.55</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>0.54</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.72</v>
       </c>
       <c r="S16" t="n">
         <v>0.72</v>
       </c>
       <c r="T16" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="U16" t="n">
         <v>0.37</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>0.44</v>
       </c>
     </row>
@@ -3529,63 +3667,66 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="C17" t="n">
         <v>12.07</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>4.6</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>1.68</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>1.41</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>1.67</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>0.3</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>0.71</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-1.12</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>-1.73</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>-2.12</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>-0.18</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>2.34</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>2</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>2.04</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>1.52</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>0.53</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.71</v>
       </c>
       <c r="S17" t="n">
         <v>0.71</v>
       </c>
       <c r="T17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="U17" t="n">
         <v>0.36</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>0.43</v>
       </c>
     </row>
@@ -3596,63 +3737,66 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>1128</v>
+      </c>
+      <c r="C18" t="n">
         <v>1126</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>1125</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>1118</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>1115</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>1111</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>1107</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>1104</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>1100</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>1094</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>1091</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>1090</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>1112</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1119</v>
       </c>
       <c r="O18" t="n">
         <v>1119</v>
       </c>
       <c r="P18" t="n">
+        <v>1119</v>
+      </c>
+      <c r="Q18" t="n">
         <v>1121</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>1120</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>1115</v>
-      </c>
-      <c r="S18" t="n">
-        <v>1111</v>
       </c>
       <c r="T18" t="n">
         <v>1111</v>
       </c>
       <c r="U18" t="n">
+        <v>1111</v>
+      </c>
+      <c r="V18" t="n">
         <v>1107</v>
       </c>
     </row>
@@ -3663,63 +3807,66 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>1145</v>
+      </c>
+      <c r="C19" t="n">
         <v>1142</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>1138</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>1125</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>1123</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>1122</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>1123</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1114</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>1100</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>1094</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1091</v>
       </c>
-      <c r="L19" t="n">
+      <c r="M19" t="n">
         <v>1090</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>1121</v>
-      </c>
-      <c r="N19" t="n">
-        <v>1130</v>
       </c>
       <c r="O19" t="n">
         <v>1130</v>
       </c>
       <c r="P19" t="n">
+        <v>1130</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1145</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>1144</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>1135</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>1129</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>1133</v>
       </c>
-      <c r="U19" t="n">
+      <c r="V19" t="n">
         <v>1129</v>
       </c>
     </row>
@@ -3734,68 +3881,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:V37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46079</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45988</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45806</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45715</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45624</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45442</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45351</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45260</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45078</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>44987</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44896</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44714</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44623</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44532</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44350</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44259</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44168</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>43979</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43888</v>
       </c>
-      <c r="U1" s="1" t="n">
+      <c r="V1" s="1" t="n">
         <v>43797</v>
       </c>
     </row>
@@ -3806,63 +3956,66 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>47268</v>
+      </c>
+      <c r="C2" t="n">
         <v>19025</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>5240</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>5338</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>3453</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1870</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>-109</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>-441</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>-1234</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>-4403</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>-2507</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>-195</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>7195</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>4569</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>2306</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>3141</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>1406</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>803</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>1720</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>915</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>508</v>
       </c>
     </row>
@@ -3873,63 +4026,66 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>6862</v>
+      </c>
+      <c r="C3" t="n">
         <v>4498</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>2212</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>6203</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>4109</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>2030</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>5794</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>3839</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>1915</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>5819</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>3863</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1921</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>5234</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>3413</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1671</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>4593</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>3036</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>1487</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>4083</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>2661</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>1296</v>
       </c>
     </row>
@@ -3940,63 +4096,66 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>954</v>
+      </c>
+      <c r="C4" t="n">
         <v>599</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>290</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>722</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>469</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>220</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>620</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>401</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>188</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>448</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>303</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>146</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>378</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>247</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>118</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>285</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>189</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>92</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>239</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>157</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>72</v>
       </c>
     </row>
@@ -4007,63 +4166,66 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>-19953</v>
+      </c>
+      <c r="C5" t="n">
         <v>-8298</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>-871</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>-123</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>338</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-817</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>-2562</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>-1759</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>-501</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>2728</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>2910</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1842</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>-906</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>-44</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>67</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>-340</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>533</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>251</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>-461</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>104</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>-208</v>
       </c>
     </row>
@@ -4074,63 +4236,66 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>-212</v>
+      </c>
+      <c r="C6" t="n">
         <v>88</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>150</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>148</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>-132</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>170</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-125</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>-57</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>111</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>-3406</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>-2896</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>-1697</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>-1146</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>-900</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>-344</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>814</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>629</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>86</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>-286</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>-90</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>175</v>
       </c>
     </row>
@@ -4141,63 +4306,66 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>3329</v>
+      </c>
+      <c r="C7" t="n">
         <v>928</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>156</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>38</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>-714</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>-241</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>846</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>573</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>271</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>-1764</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>-1795</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>-1056</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>382</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>107</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>-42</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>-309</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>-777</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>-753</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>700</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>257</v>
       </c>
-      <c r="U7" t="n">
+      <c r="V7" t="n">
         <v>178</v>
       </c>
     </row>
@@ -4208,32 +4376,32 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>2139</v>
+      </c>
+      <c r="C8" t="n">
         <v>1469</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>449</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>-681</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>-321</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-161</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>769</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>706</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>579</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
@@ -4265,6 +4433,9 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4275,26 +4446,26 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>5203</v>
+      </c>
+      <c r="C9" t="n">
         <v>2106</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>547</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>-681</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
       <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>132</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>769</v>
       </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -4332,6 +4503,9 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4342,63 +4516,66 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>112</v>
+      </c>
+      <c r="C10" t="n">
         <v>-101</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>238</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>356</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>188</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>173</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>304</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>157</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>72</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>57</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-22</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-18</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>141</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>91</v>
-      </c>
-      <c r="O10" t="n">
-        <v>25</v>
       </c>
       <c r="P10" t="n">
         <v>25</v>
       </c>
       <c r="Q10" t="n">
+        <v>25</v>
+      </c>
+      <c r="R10" t="n">
         <v>4</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>18</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>34</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-4</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4409,63 +4586,66 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>45702</v>
+      </c>
+      <c r="C11" t="n">
         <v>20314</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>8411</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>11795</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>7186</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>3244</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>5102</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>2620</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>1401</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>1310</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>1286</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>943</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>11404</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>7566</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>3938</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>8584</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>5024</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>1967</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>6035</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>4012</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>2011</v>
       </c>
     </row>
@@ -4476,63 +4656,66 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>-19602</v>
+      </c>
+      <c r="C12" t="n">
         <v>-11776</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>-5389</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>-10199</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>-7261</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>-3206</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-5266</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-3180</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>-1796</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>-6215</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>-4654</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>-2449</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>-8454</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>-5876</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>-3265</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>-8015</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>-5756</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>-2738</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>-5943</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>-3999</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>-1943</v>
       </c>
     </row>
@@ -4543,63 +4726,66 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>-4072</v>
+      </c>
+      <c r="C13" t="n">
         <v>-1120</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>-255</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>-1203</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>-816</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>-377</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>-1110</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>-465</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>-199</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>-496</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>-293</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>-90</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>-1359</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>-922</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>-528</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>-1919</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>-1349</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>-1002</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>-793</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>-566</v>
       </c>
-      <c r="U13" t="n">
+      <c r="V13" t="n">
         <v>-407</v>
       </c>
     </row>
@@ -4610,63 +4796,66 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>2989</v>
+      </c>
+      <c r="C14" t="n">
         <v>2256</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>878</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>1294</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>1028</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>65</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>267</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>234</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>85</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>248</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>64</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>2</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>104</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>66</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>55</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>335</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>176</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>40</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>140</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>105</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>22</v>
       </c>
     </row>
@@ -4677,63 +4866,66 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>1233</v>
+      </c>
+      <c r="C15" t="n">
         <v>701</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>268</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>1249</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>874</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>428</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>1433</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>726</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>374</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>1170</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>765</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>358</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>964</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>631</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>313</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>1024</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>746</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>216</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>636</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>523</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>163</v>
       </c>
     </row>
@@ -4744,63 +4936,66 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>-236</v>
+      </c>
+      <c r="C16" t="n">
         <v>-180</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>-96</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>-30</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>-125</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>-58</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>-35</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>-24</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>-22</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>-90</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>-71</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>-91</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>-162</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>-140</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>-77</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>47</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>31</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>21</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>-48</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>-21</v>
       </c>
-      <c r="U16" t="n">
+      <c r="V16" t="n">
         <v>-12</v>
       </c>
     </row>
@@ -4811,63 +5006,66 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>-19688</v>
+      </c>
+      <c r="C17" t="n">
         <v>-10119</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>-4594</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>-8889</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>-6300</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>-3148</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>-4711</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>-2709</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>-1558</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>-5361</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>-4181</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>-2266</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-7761</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>-5176</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>-2485</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>-8055</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>-5974</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>-3418</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>-4851</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>-2899</v>
       </c>
-      <c r="U17" t="n">
+      <c r="V17" t="n">
         <v>-1189</v>
       </c>
     </row>
@@ -4878,80 +5076,83 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>-9380</v>
+      </c>
+      <c r="C18" t="n">
         <v>-4626</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>-2943</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>-3604</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>-2626</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>-84</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>-1816</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>-1101</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>-53</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>-706</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>-53</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>-20</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>-2008</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>-1981</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>-1949</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>-1344</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>-103</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>-84</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>-4286</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>-1676</v>
       </c>
-      <c r="U18" t="n">
+      <c r="V18" t="n">
         <v>-1415</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Payments for Repurchase of Common Stock</t>
+          <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-650</v>
+        <v>-762</v>
       </c>
       <c r="C19" t="n">
-        <v>-300</v>
+        <v>-545</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-367</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -4969,25 +5170,25 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-425</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-425</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-425</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1648</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-667</v>
+        <v>-116</v>
       </c>
       <c r="O19" t="n">
-        <v>-259</v>
+        <v>-112</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-102</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -4996,29 +5197,32 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-203</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-159</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-89</v>
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
+          <t>Payments for Repurchase of Common Stock</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-545</v>
+        <v>-650</v>
       </c>
       <c r="C20" t="n">
-        <v>-367</v>
+        <v>-650</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -5039,22 +5243,22 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-425</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-425</v>
       </c>
       <c r="M20" t="n">
-        <v>-116</v>
+        <v>-425</v>
       </c>
       <c r="N20" t="n">
-        <v>-112</v>
+        <v>-1648</v>
       </c>
       <c r="O20" t="n">
-        <v>-102</v>
+        <v>-667</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-259</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -5066,10 +5270,13 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-203</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-159</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-89</v>
       </c>
     </row>
     <row r="21">
@@ -5079,50 +5286,50 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>-437</v>
+      </c>
+      <c r="C21" t="n">
         <v>-266</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>-134</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>-392</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>-261</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>-131</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>-384</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>-256</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>-129</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>-378</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>-252</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>-126</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>-335</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>-224</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>-112</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
@@ -5136,6 +5343,9 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5152,34 +5362,34 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
         <v>4430</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>2682</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>999</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>6716</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>5221</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>3349</v>
-      </c>
-      <c r="M22" t="n">
-        <v>2000</v>
       </c>
       <c r="N22" t="n">
         <v>2000</v>
@@ -5188,23 +5398,26 @@
         <v>2000</v>
       </c>
       <c r="P22" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q22" t="n">
         <v>1188</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
         <v>5000</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1250</v>
       </c>
       <c r="U22" t="n">
         <v>1250</v>
       </c>
+      <c r="V22" t="n">
+        <v>1250</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -5213,63 +5426,66 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>583</v>
+      </c>
+      <c r="C23" t="n">
         <v>175</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>-1</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>-220</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>-121</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>-207</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>-40</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>-18</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>-114</v>
       </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
       <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
         <v>19</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>-99</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>99</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>110</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>-13</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>-142</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>17</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>-33</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>147</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>151</v>
       </c>
-      <c r="U23" t="n">
+      <c r="V23" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5280,63 +5496,66 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>-10646</v>
+      </c>
+      <c r="C24" t="n">
         <v>-5912</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>-3745</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>214</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>-326</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>-422</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>-1368</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>-458</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>-352</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>5095</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>4434</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>2632</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>-2140</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>-979</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>-513</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>-437</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>-209</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>-214</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>-135</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>-1207</v>
       </c>
-      <c r="U24" t="n">
+      <c r="V24" t="n">
         <v>-992</v>
       </c>
     </row>
@@ -5347,65 +5566,68 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>8</v>
+      </c>
+      <c r="C25" t="n">
         <v>5</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>14</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>-3</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>-49</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>-29</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>-15</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>-8</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>-1</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>-13</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>9</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>-6</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>-71</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>-16</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>-6</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>44</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>43</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>27</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>-8</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-14</v>
       </c>
       <c r="U25" t="n">
         <v>-14</v>
       </c>
+      <c r="V25" t="n">
+        <v>-14</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5414,63 +5636,66 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>15376</v>
+      </c>
+      <c r="C26" t="n">
         <v>4288</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>86</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>3117</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>511</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>-355</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>-992</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>-555</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>-510</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>1031</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>1548</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>1303</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>1432</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>1395</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>934</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>136</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>-1116</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>-1638</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>1041</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>-108</v>
       </c>
-      <c r="U26" t="n">
+      <c r="V26" t="n">
         <v>-184</v>
       </c>
     </row>
@@ -5487,7 +5712,7 @@
         <v>9646</v>
       </c>
       <c r="D27" t="n">
-        <v>7052</v>
+        <v>9646</v>
       </c>
       <c r="E27" t="n">
         <v>7052</v>
@@ -5496,7 +5721,7 @@
         <v>7052</v>
       </c>
       <c r="G27" t="n">
-        <v>8656</v>
+        <v>7052</v>
       </c>
       <c r="H27" t="n">
         <v>8656</v>
@@ -5505,7 +5730,7 @@
         <v>8656</v>
       </c>
       <c r="J27" t="n">
-        <v>8339</v>
+        <v>8656</v>
       </c>
       <c r="K27" t="n">
         <v>8339</v>
@@ -5514,7 +5739,7 @@
         <v>8339</v>
       </c>
       <c r="M27" t="n">
-        <v>7829</v>
+        <v>8339</v>
       </c>
       <c r="N27" t="n">
         <v>7829</v>
@@ -5523,7 +5748,7 @@
         <v>7829</v>
       </c>
       <c r="P27" t="n">
-        <v>7690</v>
+        <v>7829</v>
       </c>
       <c r="Q27" t="n">
         <v>7690</v>
@@ -5532,7 +5757,7 @@
         <v>7690</v>
       </c>
       <c r="S27" t="n">
-        <v>7279</v>
+        <v>7690</v>
       </c>
       <c r="T27" t="n">
         <v>7279</v>
@@ -5540,6 +5765,9 @@
       <c r="U27" t="n">
         <v>7279</v>
       </c>
+      <c r="V27" t="n">
+        <v>7279</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5548,11 +5776,11 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>32</v>
+      </c>
+      <c r="C28" t="n">
         <v>11</v>
       </c>
-      <c r="C28" t="n">
-        <v>0</v>
-      </c>
       <c r="D28" t="n">
         <v>0</v>
       </c>
@@ -5605,6 +5833,9 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5621,23 +5852,23 @@
         <v>0</v>
       </c>
       <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
         <v>-206</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>-204</v>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
       <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
         <v>-435</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>-799</v>
       </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
@@ -5672,6 +5903,9 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5697,48 +5931,51 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
         <v>-127</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>-82</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>-56</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>-112</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>-76</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>-47</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>-132</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>-105</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>-78</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>-139</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>-123</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>-97</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>-49</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>-29</v>
       </c>
-      <c r="U30" t="n">
+      <c r="V30" t="n">
         <v>-11</v>
       </c>
     </row>
@@ -5773,14 +6010,14 @@
         <v>0</v>
       </c>
       <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
         <v>1831</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>1430</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
@@ -5806,6 +6043,9 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5849,7 +6089,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
         <v>83</v>
@@ -5858,23 +6098,26 @@
         <v>83</v>
       </c>
       <c r="P32" t="n">
+        <v>83</v>
+      </c>
+      <c r="Q32" t="n">
         <v>1</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
         <v>-40</v>
-      </c>
-      <c r="T32" t="n">
-        <v>-42</v>
       </c>
       <c r="U32" t="n">
         <v>-42</v>
       </c>
+      <c r="V32" t="n">
+        <v>-42</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -5907,39 +6150,42 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
         <v>22</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>8</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>4</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>258</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>172</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>124</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>473</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>178</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>45</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>1157</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>1059</v>
       </c>
-      <c r="U33" t="n">
+      <c r="V33" t="n">
         <v>988</v>
       </c>
     </row>
@@ -5983,16 +6229,16 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>888</v>
-      </c>
-      <c r="N34" t="n">
-        <v>893</v>
       </c>
       <c r="O34" t="n">
         <v>893</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>893</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -6007,6 +6253,9 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6056,24 +6305,27 @@
         <v>0</v>
       </c>
       <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
         <v>54</v>
       </c>
-      <c r="P35" t="n">
+      <c r="Q35" t="n">
         <v>-94</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="R35" t="n">
         <v>-11</v>
       </c>
-      <c r="R35" t="n">
+      <c r="S35" t="n">
         <v>-24</v>
       </c>
-      <c r="S35" t="n">
+      <c r="T35" t="n">
         <v>26</v>
       </c>
-      <c r="T35" t="n">
+      <c r="U35" t="n">
         <v>38</v>
       </c>
-      <c r="U35" t="n">
+      <c r="V35" t="n">
         <v>19</v>
       </c>
     </row>
@@ -6126,21 +6378,24 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>22</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>15</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>7</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>20</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>16</v>
       </c>
-      <c r="U36" t="n">
+      <c r="V36" t="n">
         <v>10</v>
       </c>
     </row>
@@ -6202,12 +6457,15 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>-744</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>-744</v>
       </c>
       <c r="U37" t="n">
+        <v>-744</v>
+      </c>
+      <c r="V37" t="n">
         <v>-744</v>
       </c>
     </row>
